--- a/db/season2_ga.xlsx
+++ b/db/season2_ga.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elshimin/Documents/championship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07063FB0-8002-1644-9087-4E4DF0BF1B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38FFC90B-6FD6-414B-AFB0-006228B76665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17780" yWindow="740" windowWidth="16780" windowHeight="21600" xr2:uid="{8B7D528E-9A04-DA4F-937D-2E643BF934C8}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" xr2:uid="{8B7D528E-9A04-DA4F-937D-2E643BF934C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -535,9 +535,6 @@
     <t>Эзе</t>
   </si>
   <si>
-    <t>Кудрадо</t>
-  </si>
-  <si>
     <t>Диа</t>
   </si>
   <si>
@@ -589,9 +586,6 @@
     <t>Фати (перешел в 6м)</t>
   </si>
   <si>
-    <t>Атлетик (Бильбао)</t>
-  </si>
-  <si>
     <t>Леау</t>
   </si>
   <si>
@@ -601,9 +595,6 @@
     <t>Сансет</t>
   </si>
   <si>
-    <t>Муниан</t>
-  </si>
-  <si>
     <t>Кулушевски</t>
   </si>
   <si>
@@ -1391,6 +1382,15 @@
   </si>
   <si>
     <t>Де Лигт (пришел в 6м)</t>
+  </si>
+  <si>
+    <t>Атлетик</t>
+  </si>
+  <si>
+    <t>Куадрадо</t>
+  </si>
+  <si>
+    <t>Муниаин</t>
   </si>
 </sst>
 </file>
@@ -2174,7 +2174,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C10" s="1">
         <v>1</v>
@@ -2514,7 +2514,7 @@
         <v>4</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C25" s="1">
         <v>7</v>
@@ -2541,7 +2541,7 @@
         <v>5</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C26" s="1">
         <v>7</v>
@@ -3143,7 +3143,7 @@
         <v>5</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C54" s="1">
         <v>7</v>
@@ -5791,7 +5791,7 @@
         <v>14</v>
       </c>
       <c r="B176" s="8" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C176" s="1">
         <v>2</v>
@@ -5839,224 +5839,224 @@
         <v>3</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A178" s="1">
+    <row r="178" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="4">
         <f>A177+1</f>
         <v>16</v>
       </c>
-      <c r="B178" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="C178" s="1">
-        <v>0</v>
-      </c>
-      <c r="D178" s="22">
-        <v>0</v>
-      </c>
-      <c r="E178" s="3">
-        <v>0</v>
-      </c>
-      <c r="F178" s="22">
-        <v>1</v>
-      </c>
-      <c r="G178" s="22">
-        <v>0</v>
-      </c>
-      <c r="H178" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="179" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="4">
-        <f>A178+1</f>
-        <v>17</v>
-      </c>
-      <c r="B179" s="9" t="s">
+      <c r="B178" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="C179" s="4">
-        <v>7</v>
-      </c>
-      <c r="D179" s="24">
-        <v>0</v>
-      </c>
-      <c r="E179" s="6">
-        <v>0</v>
-      </c>
-      <c r="F179" s="24">
-        <v>8</v>
-      </c>
-      <c r="G179" s="24">
-        <v>0</v>
-      </c>
-      <c r="H179" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="D180">
-        <f>SUM(D163:D179)</f>
+      <c r="C178" s="4">
+        <v>7</v>
+      </c>
+      <c r="D178" s="24">
+        <v>0</v>
+      </c>
+      <c r="E178" s="6">
+        <v>0</v>
+      </c>
+      <c r="F178" s="24">
+        <v>8</v>
+      </c>
+      <c r="G178" s="24">
+        <v>0</v>
+      </c>
+      <c r="H178" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D179">
+        <f>SUM(D163:D178)</f>
         <v>13</v>
       </c>
-      <c r="E180">
-        <f>SUM(E163:E179)</f>
+      <c r="E179">
+        <f>SUM(E163:E178)</f>
         <v>10</v>
       </c>
-      <c r="G180">
-        <f>SUM(G163:G179)</f>
+      <c r="G179">
+        <f>SUM(G163:G178)</f>
         <v>26</v>
       </c>
-      <c r="H180">
-        <f>SUM(H163:H179)</f>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="181" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+      <c r="H179">
+        <f>SUM(H163:H178)</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B181" s="11"/>
+      <c r="C181" s="11"/>
+      <c r="D181" s="11"/>
+      <c r="E181" s="11"/>
+      <c r="F181" s="11"/>
+      <c r="G181" s="11"/>
+      <c r="H181" s="12"/>
+    </row>
     <row r="182" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="B182" s="11"/>
-      <c r="C182" s="11"/>
+      <c r="A182" s="13"/>
+      <c r="B182" s="14"/>
+      <c r="C182" s="10" t="s">
+        <v>0</v>
+      </c>
       <c r="D182" s="11"/>
-      <c r="E182" s="11"/>
-      <c r="F182" s="11"/>
+      <c r="E182" s="12"/>
+      <c r="F182" s="11" t="s">
+        <v>63</v>
+      </c>
       <c r="G182" s="11"/>
       <c r="H182" s="12"/>
     </row>
     <row r="183" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="13"/>
-      <c r="B183" s="14"/>
-      <c r="C183" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D183" s="11"/>
-      <c r="E183" s="12"/>
-      <c r="F183" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G183" s="11"/>
-      <c r="H183" s="12"/>
-    </row>
-    <row r="184" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B184" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C184" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D184" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E184" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="F184" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="G184" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H184" s="18" t="s">
-        <v>3</v>
+      <c r="A183" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B183" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C183" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D183" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E183" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="F183" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="G183" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H183" s="18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A184" s="19">
+        <v>1</v>
+      </c>
+      <c r="B184" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C184" s="19">
+        <v>7</v>
+      </c>
+      <c r="D184" s="20">
+        <v>3</v>
+      </c>
+      <c r="E184" s="21">
+        <v>4</v>
+      </c>
+      <c r="F184" s="20">
+        <v>8</v>
+      </c>
+      <c r="G184" s="23">
+        <v>3</v>
+      </c>
+      <c r="H184" s="21">
+        <v>4</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A185" s="19">
-        <v>1</v>
-      </c>
-      <c r="B185" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C185" s="19">
-        <v>7</v>
-      </c>
-      <c r="D185" s="20">
-        <v>3</v>
-      </c>
-      <c r="E185" s="21">
-        <v>4</v>
-      </c>
-      <c r="F185" s="20">
-        <v>8</v>
-      </c>
-      <c r="G185" s="23">
-        <v>3</v>
-      </c>
-      <c r="H185" s="21">
-        <v>4</v>
+      <c r="A185" s="1">
+        <f>A184+1</f>
+        <v>2</v>
+      </c>
+      <c r="B185" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C185" s="1">
+        <v>6</v>
+      </c>
+      <c r="D185" s="2">
+        <v>7</v>
+      </c>
+      <c r="E185" s="3">
+        <v>1</v>
+      </c>
+      <c r="F185" s="22">
+        <v>7</v>
+      </c>
+      <c r="G185" s="22">
+        <v>6</v>
+      </c>
+      <c r="H185" s="3">
+        <v>2</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
-        <f>A185+1</f>
-        <v>2</v>
+        <f t="shared" ref="A186:A188" si="16">A185+1</f>
+        <v>3</v>
       </c>
       <c r="B186" s="8" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C186" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D186" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E186" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F186" s="22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G186" s="22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H186" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
-        <f t="shared" ref="A187:A189" si="16">A186+1</f>
-        <v>3</v>
+        <f t="shared" si="16"/>
+        <v>4</v>
       </c>
       <c r="B187" s="8" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C187" s="1">
-        <v>4</v>
-      </c>
-      <c r="D187" s="2">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="D187" s="22">
+        <v>2</v>
       </c>
       <c r="E187" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F187" s="22">
         <v>8</v>
       </c>
       <c r="G187" s="22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H187" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
         <f t="shared" si="16"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B188" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C188" s="1">
         <v>7</v>
       </c>
       <c r="D188" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E188" s="3">
         <v>1</v>
@@ -6065,34 +6065,34 @@
         <v>8</v>
       </c>
       <c r="G188" s="22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H188" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
-        <f t="shared" si="16"/>
-        <v>5</v>
+        <f t="shared" ref="A189:A192" si="17">A188+1</f>
+        <v>6</v>
       </c>
       <c r="B189" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C189" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D189" s="22">
         <v>1</v>
       </c>
       <c r="E189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F189" s="22">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G189" s="22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H189" s="3">
         <v>0</v>
@@ -6100,26 +6100,26 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
-        <f t="shared" ref="A190:A193" si="17">A189+1</f>
-        <v>6</v>
+        <f t="shared" si="17"/>
+        <v>7</v>
       </c>
       <c r="B190" s="8" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="C190" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D190" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E190" s="3">
         <v>0</v>
       </c>
       <c r="F190" s="22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G190" s="22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H190" s="3">
         <v>0</v>
@@ -6128,13 +6128,13 @@
     <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <f t="shared" si="17"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B191" s="8" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C191" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D191" s="22">
         <v>0</v>
@@ -6143,22 +6143,22 @@
         <v>0</v>
       </c>
       <c r="F191" s="22">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G191" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H191" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <f t="shared" si="17"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B192" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C192" s="1">
         <v>6</v>
@@ -6170,7 +6170,7 @@
         <v>0</v>
       </c>
       <c r="F192" s="22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G192" s="22">
         <v>1</v>
@@ -6181,14 +6181,14 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
-        <f t="shared" si="17"/>
-        <v>9</v>
+        <f>A192+1</f>
+        <v>10</v>
       </c>
       <c r="B193" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C193" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D193" s="22">
         <v>0</v>
@@ -6197,22 +6197,22 @@
         <v>0</v>
       </c>
       <c r="F193" s="22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G193" s="22">
         <v>1</v>
       </c>
       <c r="H193" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
-        <f>A193+1</f>
-        <v>10</v>
+        <f t="shared" ref="A194:A195" si="18">A193+1</f>
+        <v>11</v>
       </c>
       <c r="B194" s="8" t="s">
-        <v>144</v>
+        <v>438</v>
       </c>
       <c r="C194" s="1">
         <v>7</v>
@@ -6221,13 +6221,13 @@
         <v>0</v>
       </c>
       <c r="E194" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F194" s="22">
         <v>8</v>
       </c>
       <c r="G194" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H194" s="3">
         <v>0</v>
@@ -6235,11 +6235,11 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
-        <f t="shared" ref="A195:A196" si="18">A194+1</f>
-        <v>11</v>
+        <f t="shared" si="18"/>
+        <v>12</v>
       </c>
       <c r="B195" s="8" t="s">
-        <v>441</v>
+        <v>145</v>
       </c>
       <c r="C195" s="1">
         <v>7</v>
@@ -6248,13 +6248,13 @@
         <v>0</v>
       </c>
       <c r="E195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F195" s="22">
         <v>8</v>
       </c>
       <c r="G195" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H195" s="3">
         <v>0</v>
@@ -6262,14 +6262,14 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
-        <f t="shared" si="18"/>
-        <v>12</v>
+        <f t="shared" ref="A196:A197" si="19">A195+1</f>
+        <v>13</v>
       </c>
       <c r="B196" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C196" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D196" s="22">
         <v>0</v>
@@ -6278,241 +6278,241 @@
         <v>0</v>
       </c>
       <c r="F196" s="22">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G196" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H196" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A197" s="1">
-        <f t="shared" ref="A197:A198" si="19">A196+1</f>
-        <v>13</v>
-      </c>
-      <c r="B197" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="C197" s="1">
-        <v>0</v>
-      </c>
-      <c r="D197" s="22">
-        <v>0</v>
-      </c>
-      <c r="E197" s="3">
-        <v>0</v>
-      </c>
-      <c r="F197" s="22">
-        <v>1</v>
-      </c>
-      <c r="G197" s="22">
-        <v>0</v>
-      </c>
-      <c r="H197" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A198" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="4">
         <f t="shared" si="19"/>
         <v>14</v>
       </c>
-      <c r="B198" s="9" t="s">
+      <c r="B197" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="C198" s="4">
-        <v>7</v>
-      </c>
-      <c r="D198" s="24">
-        <v>0</v>
-      </c>
-      <c r="E198" s="6">
-        <v>1</v>
-      </c>
-      <c r="F198" s="24">
-        <v>8</v>
-      </c>
-      <c r="G198" s="24">
-        <v>0</v>
-      </c>
-      <c r="H198" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="D199">
-        <f>SUM(D185:D198)</f>
+      <c r="C197" s="4">
+        <v>7</v>
+      </c>
+      <c r="D197" s="24">
+        <v>0</v>
+      </c>
+      <c r="E197" s="6">
+        <v>1</v>
+      </c>
+      <c r="F197" s="24">
+        <v>8</v>
+      </c>
+      <c r="G197" s="24">
+        <v>0</v>
+      </c>
+      <c r="H197" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D198">
+        <f>SUM(D184:D197)</f>
         <v>17</v>
       </c>
-      <c r="E199">
-        <f>SUM(E185:E198)</f>
+      <c r="E198">
+        <f>SUM(E184:E197)</f>
         <v>12</v>
       </c>
-      <c r="G199">
-        <f>SUM(G185:G198)</f>
+      <c r="G198">
+        <f>SUM(G184:G197)</f>
         <v>20</v>
       </c>
-      <c r="H199">
-        <f>SUM(H185:H198)</f>
+      <c r="H198">
+        <f>SUM(H184:H197)</f>
         <v>14</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A200" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B200" s="11"/>
+      <c r="C200" s="11"/>
+      <c r="D200" s="11"/>
+      <c r="E200" s="11"/>
+      <c r="F200" s="11"/>
+      <c r="G200" s="11"/>
+      <c r="H200" s="12"/>
+    </row>
     <row r="201" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A201" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="B201" s="11"/>
-      <c r="C201" s="11"/>
+      <c r="A201" s="13"/>
+      <c r="B201" s="14"/>
+      <c r="C201" s="10" t="s">
+        <v>0</v>
+      </c>
       <c r="D201" s="11"/>
-      <c r="E201" s="11"/>
-      <c r="F201" s="11"/>
+      <c r="E201" s="12"/>
+      <c r="F201" s="11" t="s">
+        <v>63</v>
+      </c>
       <c r="G201" s="11"/>
       <c r="H201" s="12"/>
     </row>
     <row r="202" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="13"/>
-      <c r="B202" s="14"/>
-      <c r="C202" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D202" s="11"/>
-      <c r="E202" s="12"/>
-      <c r="F202" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G202" s="11"/>
-      <c r="H202" s="12"/>
-    </row>
-    <row r="203" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A203" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B203" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C203" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D203" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E203" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="F203" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="G203" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H203" s="18" t="s">
-        <v>3</v>
+      <c r="A202" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B202" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C202" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D202" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E202" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="F202" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="G202" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H202" s="18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A203" s="19">
+        <v>1</v>
+      </c>
+      <c r="B203" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C203" s="19">
+        <v>2</v>
+      </c>
+      <c r="D203" s="20">
+        <v>0</v>
+      </c>
+      <c r="E203" s="21">
+        <v>0</v>
+      </c>
+      <c r="F203" s="23">
+        <v>0</v>
+      </c>
+      <c r="G203" s="20">
+        <v>0</v>
+      </c>
+      <c r="H203" s="21">
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A204" s="19">
-        <v>1</v>
-      </c>
-      <c r="B204" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C204" s="19">
-        <v>2</v>
-      </c>
-      <c r="D204" s="20">
-        <v>0</v>
-      </c>
-      <c r="E204" s="21">
-        <v>0</v>
-      </c>
-      <c r="F204" s="23">
-        <v>0</v>
-      </c>
-      <c r="G204" s="20">
-        <v>0</v>
-      </c>
-      <c r="H204" s="21">
-        <v>0</v>
+      <c r="A204" s="1">
+        <f>A203+1</f>
+        <v>2</v>
+      </c>
+      <c r="B204" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C204" s="1">
+        <v>7</v>
+      </c>
+      <c r="D204" s="2">
+        <v>5</v>
+      </c>
+      <c r="E204" s="3">
+        <v>3</v>
+      </c>
+      <c r="F204" s="22">
+        <v>8</v>
+      </c>
+      <c r="G204" s="2">
+        <v>5</v>
+      </c>
+      <c r="H204" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
-        <f>A204+1</f>
-        <v>2</v>
+        <f t="shared" ref="A205:A214" si="20">A204+1</f>
+        <v>3</v>
       </c>
       <c r="B205" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C205" s="1">
         <v>7</v>
       </c>
       <c r="D205" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E205" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F205" s="22">
         <v>8</v>
       </c>
       <c r="G205" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H205" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
-        <f t="shared" ref="A206:A215" si="20">A205+1</f>
-        <v>3</v>
+        <f t="shared" si="20"/>
+        <v>4</v>
       </c>
       <c r="B206" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C206" s="1">
         <v>7</v>
       </c>
       <c r="D206" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E206" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F206" s="22">
         <v>8</v>
       </c>
       <c r="G206" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H206" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <f t="shared" si="20"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B207" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C207" s="1">
         <v>7</v>
       </c>
-      <c r="D207" s="2">
-        <v>7</v>
+      <c r="D207" s="22">
+        <v>5</v>
       </c>
       <c r="E207" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F207" s="22">
         <v>8</v>
       </c>
-      <c r="G207" s="2">
+      <c r="G207" s="22">
         <v>6</v>
       </c>
       <c r="H207" s="3">
@@ -6522,25 +6522,25 @@
     <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
         <f t="shared" si="20"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B208" s="8" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="C208" s="1">
         <v>7</v>
       </c>
       <c r="D208" s="22">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E208" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F208" s="22">
         <v>8</v>
       </c>
       <c r="G208" s="22">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H208" s="3">
         <v>1</v>
@@ -6549,13 +6549,13 @@
     <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
         <f t="shared" si="20"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B209" s="8" t="s">
-        <v>439</v>
+        <v>161</v>
       </c>
       <c r="C209" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D209" s="22">
         <v>0</v>
@@ -6564,7 +6564,7 @@
         <v>0</v>
       </c>
       <c r="F209" s="22">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G209" s="22">
         <v>0</v>
@@ -6576,13 +6576,13 @@
     <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
         <f t="shared" si="20"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B210" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C210" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D210" s="22">
         <v>0</v>
@@ -6591,10 +6591,10 @@
         <v>0</v>
       </c>
       <c r="F210" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G210" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H210" s="3">
         <v>1</v>
@@ -6603,64 +6603,64 @@
     <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
         <f t="shared" si="20"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B211" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C211" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D211" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E211" s="3">
         <v>0</v>
       </c>
       <c r="F211" s="22">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G211" s="22">
         <v>1</v>
       </c>
       <c r="H211" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <f t="shared" si="20"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B212" s="8" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C212" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D212" s="22">
         <v>1</v>
       </c>
       <c r="E212" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F212" s="22">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G212" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H212" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <f t="shared" si="20"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B213" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C213" s="1">
         <v>5</v>
@@ -6669,176 +6669,176 @@
         <v>1</v>
       </c>
       <c r="E213" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F213" s="22">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G213" s="22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H213" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A214" s="1">
-        <f t="shared" si="20"/>
-        <v>11</v>
-      </c>
-      <c r="B214" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C214" s="1">
-        <v>5</v>
-      </c>
-      <c r="D214" s="22">
-        <v>1</v>
-      </c>
-      <c r="E214" s="3">
-        <v>3</v>
-      </c>
-      <c r="F214" s="22">
-        <v>0</v>
-      </c>
-      <c r="G214" s="22">
-        <v>0</v>
-      </c>
-      <c r="H214" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="215" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="4">
+    <row r="214" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A214" s="4">
         <f t="shared" si="20"/>
         <v>12</v>
       </c>
-      <c r="B215" s="9" t="s">
+      <c r="B214" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="C215" s="4">
-        <v>1</v>
-      </c>
-      <c r="D215" s="24">
-        <v>1</v>
-      </c>
-      <c r="E215" s="6">
-        <v>0</v>
-      </c>
-      <c r="F215" s="24">
-        <v>0</v>
-      </c>
-      <c r="G215" s="24">
-        <v>0</v>
-      </c>
-      <c r="H215" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="D216">
-        <f>SUM(D204:D215)</f>
+      <c r="C214" s="4">
+        <v>1</v>
+      </c>
+      <c r="D214" s="24">
+        <v>1</v>
+      </c>
+      <c r="E214" s="6">
+        <v>0</v>
+      </c>
+      <c r="F214" s="24">
+        <v>0</v>
+      </c>
+      <c r="G214" s="24">
+        <v>0</v>
+      </c>
+      <c r="H214" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D215">
+        <f>SUM(D203:D214)</f>
         <v>25</v>
       </c>
-      <c r="E216">
-        <f>SUM(E204:E215)</f>
+      <c r="E215">
+        <f>SUM(E203:E214)</f>
         <v>19</v>
       </c>
-      <c r="G216">
-        <f>SUM(G204:G215)</f>
+      <c r="G215">
+        <f>SUM(G203:G214)</f>
         <v>24</v>
       </c>
-      <c r="H216">
-        <f>SUM(H204:H215)</f>
+      <c r="H215">
+        <f>SUM(H203:H214)</f>
         <v>17</v>
       </c>
     </row>
-    <row r="217" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="216" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="217" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A217" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="B217" s="11"/>
+      <c r="C217" s="11"/>
+      <c r="D217" s="11"/>
+      <c r="E217" s="11"/>
+      <c r="F217" s="11"/>
+      <c r="G217" s="11"/>
+      <c r="H217" s="12"/>
+    </row>
     <row r="218" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A218" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="B218" s="11"/>
-      <c r="C218" s="11"/>
+      <c r="A218" s="13"/>
+      <c r="B218" s="14"/>
+      <c r="C218" s="10" t="s">
+        <v>0</v>
+      </c>
       <c r="D218" s="11"/>
-      <c r="E218" s="11"/>
-      <c r="F218" s="11"/>
+      <c r="E218" s="12"/>
+      <c r="F218" s="11" t="s">
+        <v>63</v>
+      </c>
       <c r="G218" s="11"/>
       <c r="H218" s="12"/>
     </row>
     <row r="219" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="13"/>
-      <c r="B219" s="14"/>
-      <c r="C219" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D219" s="11"/>
-      <c r="E219" s="12"/>
-      <c r="F219" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G219" s="11"/>
-      <c r="H219" s="12"/>
-    </row>
-    <row r="220" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A220" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B220" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C220" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D220" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E220" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="F220" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="G220" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H220" s="18" t="s">
-        <v>3</v>
+      <c r="A219" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B219" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C219" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D219" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E219" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="F219" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="G219" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H219" s="18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A220" s="19">
+        <v>1</v>
+      </c>
+      <c r="B220" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C220" s="19">
+        <v>7</v>
+      </c>
+      <c r="D220" s="20">
+        <v>6</v>
+      </c>
+      <c r="E220" s="21">
+        <v>1</v>
+      </c>
+      <c r="F220" s="20">
+        <v>7</v>
+      </c>
+      <c r="G220" s="23">
+        <v>4</v>
+      </c>
+      <c r="H220" s="21">
+        <v>0</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A221" s="19">
-        <v>1</v>
-      </c>
-      <c r="B221" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="C221" s="19">
-        <v>7</v>
-      </c>
-      <c r="D221" s="20">
-        <v>6</v>
-      </c>
-      <c r="E221" s="21">
-        <v>1</v>
-      </c>
-      <c r="F221" s="20">
-        <v>7</v>
-      </c>
-      <c r="G221" s="23">
-        <v>4</v>
-      </c>
-      <c r="H221" s="21">
-        <v>0</v>
+      <c r="A221" s="1">
+        <f>A220+1</f>
+        <v>2</v>
+      </c>
+      <c r="B221" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C221" s="1">
+        <v>7</v>
+      </c>
+      <c r="D221" s="2">
+        <v>2</v>
+      </c>
+      <c r="E221" s="3">
+        <v>4</v>
+      </c>
+      <c r="F221" s="22">
+        <v>8</v>
+      </c>
+      <c r="G221" s="22">
+        <v>2</v>
+      </c>
+      <c r="H221" s="3">
+        <v>4</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
-        <f>A221+1</f>
-        <v>2</v>
+        <f t="shared" ref="A222:A230" si="21">A221+1</f>
+        <v>3</v>
       </c>
       <c r="B222" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C222" s="1">
         <v>7</v>
@@ -6847,67 +6847,67 @@
         <v>2</v>
       </c>
       <c r="E222" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F222" s="22">
         <v>8</v>
       </c>
       <c r="G222" s="22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H222" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
-        <f t="shared" ref="A223:A231" si="21">A222+1</f>
-        <v>3</v>
+        <f t="shared" si="21"/>
+        <v>4</v>
       </c>
       <c r="B223" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C223" s="1">
-        <v>7</v>
-      </c>
-      <c r="D223" s="2">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="D223" s="22">
+        <v>0</v>
       </c>
       <c r="E223" s="3">
         <v>1</v>
       </c>
       <c r="F223" s="22">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G223" s="22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H223" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <f t="shared" si="21"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B224" s="8" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C224" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D224" s="22">
         <v>0</v>
       </c>
       <c r="E224" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F224" s="22">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G224" s="22">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H224" s="3">
         <v>1</v>
@@ -6916,106 +6916,106 @@
     <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <f t="shared" si="21"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B225" s="8" t="s">
-        <v>173</v>
+        <v>450</v>
       </c>
       <c r="C225" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D225" s="22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E225" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F225" s="22">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G225" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H225" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <f t="shared" si="21"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B226" s="8" t="s">
         <v>166</v>
       </c>
       <c r="C226" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D226" s="22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E226" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F226" s="22">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G226" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H226" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <f t="shared" si="21"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B227" s="8" t="s">
         <v>167</v>
       </c>
       <c r="C227" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D227" s="22">
         <v>0</v>
       </c>
       <c r="E227" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F227" s="22">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G227" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H227" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <f t="shared" si="21"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B228" s="8" t="s">
         <v>168</v>
       </c>
       <c r="C228" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D228" s="22">
         <v>0</v>
       </c>
       <c r="E228" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F228" s="22">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G228" s="22">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H228" s="3">
         <v>1</v>
@@ -7024,13 +7024,13 @@
     <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <f t="shared" si="21"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B229" s="8" t="s">
         <v>169</v>
       </c>
       <c r="C229" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D229" s="22">
         <v>0</v>
@@ -7042,196 +7042,188 @@
         <v>4</v>
       </c>
       <c r="G229" s="22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H229" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <f t="shared" si="21"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B230" s="8" t="s">
         <v>170</v>
       </c>
       <c r="C230" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D230" s="22">
         <v>0</v>
       </c>
       <c r="E230" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F230" s="22">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G230" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H230" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A231" s="1">
-        <f t="shared" si="21"/>
-        <v>11</v>
-      </c>
-      <c r="B231" s="8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A231" s="4">
+        <f>A230+1</f>
+        <v>12</v>
+      </c>
+      <c r="B231" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C231" s="1">
-        <v>7</v>
-      </c>
-      <c r="D231" s="22">
-        <v>0</v>
-      </c>
-      <c r="E231" s="3">
-        <v>1</v>
-      </c>
-      <c r="F231" s="22">
-        <v>7</v>
-      </c>
-      <c r="G231" s="22">
-        <v>0</v>
-      </c>
-      <c r="H231" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="232" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A232" s="4">
-        <f>A231+1</f>
+      <c r="C231" s="4">
+        <v>7</v>
+      </c>
+      <c r="D231" s="24">
+        <v>0</v>
+      </c>
+      <c r="E231" s="6">
+        <v>0</v>
+      </c>
+      <c r="F231" s="24">
+        <v>7</v>
+      </c>
+      <c r="G231" s="24">
+        <v>0</v>
+      </c>
+      <c r="H231" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D232">
+        <f>SUM(D220:D231)</f>
         <v>12</v>
       </c>
-      <c r="B232" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="C232" s="4">
-        <v>7</v>
-      </c>
-      <c r="D232" s="24">
-        <v>0</v>
-      </c>
-      <c r="E232" s="6">
-        <v>0</v>
-      </c>
-      <c r="F232" s="24">
-        <v>7</v>
-      </c>
-      <c r="G232" s="24">
-        <v>0</v>
-      </c>
-      <c r="H232" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="D233">
-        <f>SUM(D221:D232)</f>
-        <v>12</v>
-      </c>
-      <c r="E233">
-        <f>SUM(E221:E232)</f>
+      <c r="E232">
+        <f>SUM(E220:E231)</f>
         <v>10</v>
       </c>
-      <c r="G233">
-        <f>SUM(G221:G232)</f>
+      <c r="G232">
+        <f>SUM(G220:G231)</f>
         <v>23</v>
       </c>
-      <c r="H233">
-        <f>SUM(H221:H232)</f>
+      <c r="H232">
+        <f>SUM(H220:H231)</f>
         <v>17</v>
       </c>
     </row>
-    <row r="234" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="233" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="234" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A234" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B234" s="11"/>
+      <c r="C234" s="11"/>
+      <c r="D234" s="11"/>
+      <c r="E234" s="11"/>
+      <c r="F234" s="11"/>
+      <c r="G234" s="11"/>
+      <c r="H234" s="12"/>
+    </row>
     <row r="235" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A235" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="B235" s="11"/>
-      <c r="C235" s="11"/>
+      <c r="A235" s="13"/>
+      <c r="B235" s="14"/>
+      <c r="C235" s="10" t="s">
+        <v>0</v>
+      </c>
       <c r="D235" s="11"/>
-      <c r="E235" s="11"/>
-      <c r="F235" s="11"/>
+      <c r="E235" s="12"/>
+      <c r="F235" s="11" t="s">
+        <v>64</v>
+      </c>
       <c r="G235" s="11"/>
       <c r="H235" s="12"/>
     </row>
     <row r="236" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="13"/>
-      <c r="B236" s="14"/>
-      <c r="C236" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D236" s="11"/>
-      <c r="E236" s="12"/>
-      <c r="F236" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="G236" s="11"/>
-      <c r="H236" s="12"/>
-    </row>
-    <row r="237" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A237" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B237" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C237" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D237" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E237" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="F237" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="G237" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H237" s="18" t="s">
-        <v>3</v>
-      </c>
+      <c r="A236" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B236" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C236" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D236" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E236" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="F236" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="G236" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H236" s="18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A237" s="19">
+        <v>1</v>
+      </c>
+      <c r="B237" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C237" s="19"/>
+      <c r="D237" s="20">
+        <v>8</v>
+      </c>
+      <c r="E237" s="21">
+        <v>1</v>
+      </c>
+      <c r="F237" s="20"/>
+      <c r="G237" s="23"/>
+      <c r="H237" s="21"/>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A238" s="19">
-        <v>1</v>
-      </c>
-      <c r="B238" s="7" t="s">
+      <c r="A238" s="1">
+        <f>A237+1</f>
+        <v>2</v>
+      </c>
+      <c r="B238" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="C238" s="19"/>
-      <c r="D238" s="20">
-        <v>8</v>
-      </c>
-      <c r="E238" s="21">
-        <v>1</v>
-      </c>
-      <c r="F238" s="20"/>
-      <c r="G238" s="23"/>
-      <c r="H238" s="21"/>
+      <c r="C238" s="1"/>
+      <c r="D238" s="2">
+        <v>2</v>
+      </c>
+      <c r="E238" s="3">
+        <v>5</v>
+      </c>
+      <c r="F238" s="22"/>
+      <c r="G238" s="22"/>
+      <c r="H238" s="3"/>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
-        <f>A238+1</f>
-        <v>2</v>
+        <f t="shared" ref="A239:A244" si="22">A238+1</f>
+        <v>3</v>
       </c>
       <c r="B239" s="8" t="s">
         <v>177</v>
       </c>
       <c r="C239" s="1"/>
       <c r="D239" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E239" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F239" s="22"/>
       <c r="G239" s="22"/>
@@ -7239,18 +7231,18 @@
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
-        <f t="shared" ref="A240:A245" si="22">A239+1</f>
-        <v>3</v>
+        <f t="shared" si="22"/>
+        <v>4</v>
       </c>
       <c r="B240" s="8" t="s">
         <v>178</v>
       </c>
       <c r="C240" s="1"/>
-      <c r="D240" s="2">
-        <v>0</v>
+      <c r="D240" s="22">
+        <v>2</v>
       </c>
       <c r="E240" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F240" s="22"/>
       <c r="G240" s="22"/>
@@ -7259,17 +7251,17 @@
     <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
         <f t="shared" si="22"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B241" s="8" t="s">
         <v>179</v>
       </c>
       <c r="C241" s="1"/>
       <c r="D241" s="22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E241" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F241" s="22"/>
       <c r="G241" s="22"/>
@@ -7278,7 +7270,7 @@
     <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
         <f t="shared" si="22"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B242" s="8" t="s">
         <v>180</v>
@@ -7297,7 +7289,7 @@
     <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
         <f t="shared" si="22"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B243" s="8" t="s">
         <v>181</v>
@@ -7307,214 +7299,222 @@
         <v>0</v>
       </c>
       <c r="E243" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F243" s="22"/>
       <c r="G243" s="22"/>
       <c r="H243" s="3"/>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A244" s="1">
+    <row r="244" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A244" s="4">
         <f t="shared" si="22"/>
-        <v>7</v>
-      </c>
-      <c r="B244" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B244" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="C244" s="1"/>
-      <c r="D244" s="22">
-        <v>0</v>
-      </c>
-      <c r="E244" s="3">
-        <v>1</v>
-      </c>
-      <c r="F244" s="22"/>
-      <c r="G244" s="22"/>
-      <c r="H244" s="3"/>
-    </row>
-    <row r="245" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A245" s="4">
-        <f t="shared" si="22"/>
-        <v>8</v>
-      </c>
-      <c r="B245" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="C245" s="4"/>
-      <c r="D245" s="24">
-        <v>2</v>
-      </c>
-      <c r="E245" s="6">
-        <v>0</v>
-      </c>
-      <c r="F245" s="24"/>
-      <c r="G245" s="24"/>
-      <c r="H245" s="6"/>
-    </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="D246">
-        <f>SUM(D238:D245)</f>
+      <c r="C244" s="4"/>
+      <c r="D244" s="24">
+        <v>2</v>
+      </c>
+      <c r="E244" s="6">
+        <v>0</v>
+      </c>
+      <c r="F244" s="24"/>
+      <c r="G244" s="24"/>
+      <c r="H244" s="6"/>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D245">
+        <f>SUM(D237:D244)</f>
         <v>14</v>
       </c>
-      <c r="E246">
-        <f>SUM(E238:E245)</f>
+      <c r="E245">
+        <f>SUM(E237:E244)</f>
         <v>14</v>
       </c>
-      <c r="G246">
-        <f>SUM(G238:G245)</f>
-        <v>0</v>
-      </c>
-      <c r="H246">
-        <f>SUM(H238:H245)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="247" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+      <c r="G245">
+        <f>SUM(G237:G244)</f>
+        <v>0</v>
+      </c>
+      <c r="H245">
+        <f>SUM(H237:H244)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="247" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A247" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="B247" s="11"/>
+      <c r="C247" s="11"/>
+      <c r="D247" s="11"/>
+      <c r="E247" s="11"/>
+      <c r="F247" s="11"/>
+      <c r="G247" s="11"/>
+      <c r="H247" s="12"/>
+    </row>
     <row r="248" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A248" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="B248" s="11"/>
-      <c r="C248" s="11"/>
+      <c r="A248" s="13"/>
+      <c r="B248" s="14"/>
+      <c r="C248" s="10" t="s">
+        <v>0</v>
+      </c>
       <c r="D248" s="11"/>
-      <c r="E248" s="11"/>
-      <c r="F248" s="11"/>
+      <c r="E248" s="12"/>
+      <c r="F248" s="11" t="s">
+        <v>63</v>
+      </c>
       <c r="G248" s="11"/>
       <c r="H248" s="12"/>
     </row>
     <row r="249" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A249" s="13"/>
-      <c r="B249" s="14"/>
-      <c r="C249" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D249" s="11"/>
-      <c r="E249" s="12"/>
-      <c r="F249" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G249" s="11"/>
-      <c r="H249" s="12"/>
-    </row>
-    <row r="250" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A250" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B250" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C250" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D250" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E250" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="F250" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="G250" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H250" s="18" t="s">
-        <v>3</v>
+      <c r="A249" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B249" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C249" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D249" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E249" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="F249" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="G249" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H249" s="18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A250" s="19">
+        <v>1</v>
+      </c>
+      <c r="B250" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C250" s="19">
+        <v>7</v>
+      </c>
+      <c r="D250" s="20">
+        <v>9</v>
+      </c>
+      <c r="E250" s="21">
+        <v>3</v>
+      </c>
+      <c r="F250" s="20">
+        <v>8</v>
+      </c>
+      <c r="G250" s="23">
+        <v>8</v>
+      </c>
+      <c r="H250" s="21">
+        <v>5</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A251" s="19">
-        <v>1</v>
-      </c>
-      <c r="B251" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="C251" s="19">
-        <v>7</v>
-      </c>
-      <c r="D251" s="20">
-        <v>9</v>
-      </c>
-      <c r="E251" s="21">
-        <v>3</v>
-      </c>
-      <c r="F251" s="20">
-        <v>8</v>
-      </c>
-      <c r="G251" s="23">
-        <v>8</v>
-      </c>
-      <c r="H251" s="21">
-        <v>5</v>
+      <c r="A251" s="1">
+        <f>A250+1</f>
+        <v>2</v>
+      </c>
+      <c r="B251" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C251" s="1">
+        <v>5</v>
+      </c>
+      <c r="D251" s="2">
+        <v>6</v>
+      </c>
+      <c r="E251" s="3">
+        <v>0</v>
+      </c>
+      <c r="F251" s="22">
+        <v>6</v>
+      </c>
+      <c r="G251" s="22">
+        <v>0</v>
+      </c>
+      <c r="H251" s="3">
+        <v>3</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
-        <f>A251+1</f>
-        <v>2</v>
+        <f t="shared" ref="A252:A262" si="23">A251+1</f>
+        <v>3</v>
       </c>
       <c r="B252" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C252" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D252" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E252" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F252" s="22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G252" s="22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H252" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
-        <f t="shared" ref="A253:A262" si="23">A252+1</f>
-        <v>3</v>
+        <f t="shared" si="23"/>
+        <v>4</v>
       </c>
       <c r="B253" s="8" t="s">
-        <v>187</v>
+        <v>451</v>
       </c>
       <c r="C253" s="1">
-        <v>7</v>
-      </c>
-      <c r="D253" s="2">
+        <v>4</v>
+      </c>
+      <c r="D253" s="22">
         <v>2</v>
       </c>
       <c r="E253" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F253" s="22">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G253" s="22">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H253" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
         <f t="shared" si="23"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B254" s="8" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C254" s="1">
         <v>4</v>
       </c>
       <c r="D254" s="22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E254" s="3">
         <v>1</v>
@@ -7523,61 +7523,61 @@
         <v>4</v>
       </c>
       <c r="G254" s="22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H254" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <f t="shared" si="23"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B255" s="8" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="C255" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D255" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E255" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F255" s="22">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G255" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H255" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
         <f t="shared" si="23"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B256" s="8" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C256" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D256" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E256" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F256" s="22">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G256" s="22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H256" s="3">
         <v>0</v>
@@ -7586,25 +7586,25 @@
     <row r="257" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
         <f t="shared" si="23"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B257" s="8" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C257" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D257" s="22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E257" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F257" s="22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G257" s="22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H257" s="3">
         <v>0</v>
@@ -7613,25 +7613,25 @@
     <row r="258" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
         <f t="shared" si="23"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B258" s="8" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C258" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D258" s="22">
         <v>0</v>
       </c>
       <c r="E258" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F258" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G258" s="22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H258" s="3">
         <v>0</v>
@@ -7640,49 +7640,49 @@
     <row r="259" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
         <f t="shared" si="23"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B259" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C259" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D259" s="22">
         <v>0</v>
       </c>
       <c r="E259" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F259" s="22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G259" s="22">
         <v>0</v>
       </c>
       <c r="H259" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <f t="shared" si="23"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B260" s="8" t="s">
-        <v>193</v>
+        <v>447</v>
       </c>
       <c r="C260" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D260" s="22">
         <v>0</v>
       </c>
       <c r="E260" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F260" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G260" s="22">
         <v>0</v>
@@ -7694,10 +7694,10 @@
     <row r="261" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <f t="shared" si="23"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B261" s="8" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C261" s="1">
         <v>1</v>
@@ -7721,10 +7721,10 @@
     <row r="262" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <f t="shared" si="23"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B262" s="8" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C262" s="1">
         <v>6</v>
@@ -7748,10 +7748,10 @@
     <row r="263" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A263" s="4">
         <f>A262+1</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B263" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C263" s="4">
         <v>7</v>
@@ -7774,26 +7774,26 @@
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.2">
       <c r="D264">
-        <f>SUM(D251:D263)</f>
+        <f>SUM(D250:D263)</f>
         <v>23</v>
       </c>
       <c r="E264">
-        <f>SUM(E251:E263)</f>
+        <f>SUM(E250:E263)</f>
         <v>19</v>
       </c>
       <c r="G264">
-        <f>SUM(G251:G263)</f>
+        <f>SUM(G250:G263)</f>
         <v>23</v>
       </c>
       <c r="H264">
-        <f>SUM(H251:H263)</f>
-        <v>18</v>
+        <f>SUM(H250:H263)</f>
+        <v>19</v>
       </c>
     </row>
     <row r="265" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="266" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A266" s="10" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B266" s="11"/>
       <c r="C266" s="11"/>
@@ -7848,7 +7848,7 @@
         <v>1</v>
       </c>
       <c r="B269" s="7" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C269" s="19">
         <v>7</v>
@@ -7875,7 +7875,7 @@
         <v>2</v>
       </c>
       <c r="B270" s="8" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C270" s="1">
         <v>7</v>
@@ -7902,7 +7902,7 @@
         <v>3</v>
       </c>
       <c r="B271" s="8" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C271" s="1">
         <v>4</v>
@@ -7929,7 +7929,7 @@
         <v>4</v>
       </c>
       <c r="B272" s="8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C272" s="1">
         <v>4</v>
@@ -7956,7 +7956,7 @@
         <v>5</v>
       </c>
       <c r="B273" s="8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C273" s="1">
         <v>6</v>
@@ -8010,7 +8010,7 @@
         <v>7</v>
       </c>
       <c r="B275" s="8" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C275" s="1">
         <v>4</v>
@@ -8037,7 +8037,7 @@
         <v>8</v>
       </c>
       <c r="B276" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C276" s="1">
         <v>0</v>
@@ -8064,7 +8064,7 @@
         <v>9</v>
       </c>
       <c r="B277" s="8" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C277" s="1">
         <v>7</v>
@@ -8091,7 +8091,7 @@
         <v>10</v>
       </c>
       <c r="B278" s="8" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C278" s="1">
         <v>7</v>
@@ -8118,7 +8118,7 @@
         <v>11</v>
       </c>
       <c r="B279" s="8" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C279" s="1">
         <v>6</v>
@@ -8145,7 +8145,7 @@
         <v>12</v>
       </c>
       <c r="B280" s="9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C280" s="4">
         <v>7</v>
@@ -8187,7 +8187,7 @@
     <row r="282" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="283" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A283" s="10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B283" s="11"/>
       <c r="C283" s="11"/>
@@ -8242,7 +8242,7 @@
         <v>1</v>
       </c>
       <c r="B286" s="7" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C286" s="19">
         <v>8</v>
@@ -8269,7 +8269,7 @@
         <v>2</v>
       </c>
       <c r="B287" s="8" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C287" s="1">
         <v>8</v>
@@ -8296,7 +8296,7 @@
         <v>3</v>
       </c>
       <c r="B288" s="8" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C288" s="1">
         <v>8</v>
@@ -8323,7 +8323,7 @@
         <v>4</v>
       </c>
       <c r="B289" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C289" s="1">
         <v>5</v>
@@ -8350,7 +8350,7 @@
         <v>5</v>
       </c>
       <c r="B290" s="8" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C290" s="1">
         <v>1</v>
@@ -8377,7 +8377,7 @@
         <v>6</v>
       </c>
       <c r="B291" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C291" s="1">
         <v>8</v>
@@ -8404,7 +8404,7 @@
         <v>7</v>
       </c>
       <c r="B292" s="8" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C292" s="1">
         <v>5</v>
@@ -8431,7 +8431,7 @@
         <v>8</v>
       </c>
       <c r="B293" s="8" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C293" s="1">
         <v>3</v>
@@ -8458,7 +8458,7 @@
         <v>9</v>
       </c>
       <c r="B294" s="8" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C294" s="1">
         <v>1</v>
@@ -8485,7 +8485,7 @@
         <v>10</v>
       </c>
       <c r="B295" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C295" s="1">
         <v>3</v>
@@ -8512,7 +8512,7 @@
         <v>11</v>
       </c>
       <c r="B296" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C296" s="1">
         <v>8</v>
@@ -8539,7 +8539,7 @@
         <v>12</v>
       </c>
       <c r="B297" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C297" s="4">
         <v>8</v>
@@ -8581,7 +8581,7 @@
     <row r="299" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="300" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A300" s="10" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B300" s="11"/>
       <c r="C300" s="11"/>
@@ -8636,7 +8636,7 @@
         <v>1</v>
       </c>
       <c r="B303" s="7" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C303" s="19">
         <v>8</v>
@@ -8657,7 +8657,7 @@
         <v>2</v>
       </c>
       <c r="B304" s="8" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C304" s="1">
         <v>8</v>
@@ -8678,7 +8678,7 @@
         <v>3</v>
       </c>
       <c r="B305" s="8" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C305" s="1">
         <v>8</v>
@@ -8699,7 +8699,7 @@
         <v>4</v>
       </c>
       <c r="B306" s="8" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C306" s="1">
         <v>8</v>
@@ -8720,7 +8720,7 @@
         <v>5</v>
       </c>
       <c r="B307" s="8" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C307" s="1">
         <v>0</v>
@@ -8741,7 +8741,7 @@
         <v>6</v>
       </c>
       <c r="B308" s="8" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C308" s="1">
         <v>8</v>
@@ -8762,7 +8762,7 @@
         <v>7</v>
       </c>
       <c r="B309" s="9" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C309" s="4">
         <v>3</v>
@@ -8798,7 +8798,7 @@
     <row r="311" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="312" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A312" s="10" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B312" s="11"/>
       <c r="C312" s="11"/>
@@ -8853,7 +8853,7 @@
         <v>1</v>
       </c>
       <c r="B315" s="7" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C315" s="19">
         <v>0</v>
@@ -8874,7 +8874,7 @@
         <v>2</v>
       </c>
       <c r="B316" s="8" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C316" s="1">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>3</v>
       </c>
       <c r="B317" s="8" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C317" s="1">
         <v>7</v>
@@ -8916,7 +8916,7 @@
         <v>4</v>
       </c>
       <c r="B318" s="8" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C318" s="1">
         <v>7</v>
@@ -8937,7 +8937,7 @@
         <v>5</v>
       </c>
       <c r="B319" s="8" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C319" s="1">
         <v>7</v>
@@ -8958,7 +8958,7 @@
         <v>6</v>
       </c>
       <c r="B320" s="8" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C320" s="1">
         <v>7</v>
@@ -8979,7 +8979,7 @@
         <v>7</v>
       </c>
       <c r="B321" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C321" s="4">
         <v>7</v>
@@ -9015,7 +9015,7 @@
     <row r="323" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="324" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A324" s="10" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B324" s="11"/>
       <c r="C324" s="11"/>
@@ -9070,7 +9070,7 @@
         <v>1</v>
       </c>
       <c r="B327" s="7" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C327" s="19">
         <v>8</v>
@@ -9097,7 +9097,7 @@
         <v>2</v>
       </c>
       <c r="B328" s="8" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C328" s="1">
         <v>7</v>
@@ -9124,7 +9124,7 @@
         <v>3</v>
       </c>
       <c r="B329" s="8" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C329" s="1">
         <v>8</v>
@@ -9151,7 +9151,7 @@
         <v>4</v>
       </c>
       <c r="B330" s="8" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C330" s="1">
         <v>8</v>
@@ -9178,7 +9178,7 @@
         <v>5</v>
       </c>
       <c r="B331" s="8" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C331" s="1">
         <v>2</v>
@@ -9205,7 +9205,7 @@
         <v>6</v>
       </c>
       <c r="B332" s="8" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C332" s="1">
         <v>1</v>
@@ -9232,7 +9232,7 @@
         <v>7</v>
       </c>
       <c r="B333" s="8" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C333" s="1">
         <v>8</v>
@@ -9259,7 +9259,7 @@
         <v>8</v>
       </c>
       <c r="B334" s="8" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C334" s="1">
         <v>0</v>
@@ -9286,7 +9286,7 @@
         <v>9</v>
       </c>
       <c r="B335" s="8" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C335" s="1">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>10</v>
       </c>
       <c r="B336" s="8" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C336" s="1">
         <v>3</v>
@@ -9340,7 +9340,7 @@
         <v>11</v>
       </c>
       <c r="B337" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C337" s="4">
         <v>6</v>
@@ -9382,7 +9382,7 @@
     <row r="339" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="340" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A340" s="10" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B340" s="11"/>
       <c r="C340" s="11"/>
@@ -9437,7 +9437,7 @@
         <v>1</v>
       </c>
       <c r="B343" s="7" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C343" s="19">
         <v>6</v>
@@ -9464,7 +9464,7 @@
         <v>2</v>
       </c>
       <c r="B344" s="8" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C344" s="1">
         <v>7</v>
@@ -9491,7 +9491,7 @@
         <v>3</v>
       </c>
       <c r="B345" s="8" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C345" s="1">
         <v>4</v>
@@ -9518,7 +9518,7 @@
         <v>4</v>
       </c>
       <c r="B346" s="8" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C346" s="1">
         <v>4</v>
@@ -9545,7 +9545,7 @@
         <v>5</v>
       </c>
       <c r="B347" s="8" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C347" s="1">
         <v>3</v>
@@ -9572,7 +9572,7 @@
         <v>6</v>
       </c>
       <c r="B348" s="8" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C348" s="1">
         <v>7</v>
@@ -9599,7 +9599,7 @@
         <v>7</v>
       </c>
       <c r="B349" s="8" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C349" s="1">
         <v>7</v>
@@ -9626,7 +9626,7 @@
         <v>8</v>
       </c>
       <c r="B350" s="8" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C350" s="1">
         <v>2</v>
@@ -9653,7 +9653,7 @@
         <v>9</v>
       </c>
       <c r="B351" s="9" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C351" s="4">
         <v>0</v>
@@ -9695,7 +9695,7 @@
     <row r="353" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="354" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A354" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B354" s="11"/>
       <c r="C354" s="11"/>
@@ -9750,7 +9750,7 @@
         <v>1</v>
       </c>
       <c r="B357" s="7" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C357" s="19">
         <v>8</v>
@@ -9777,7 +9777,7 @@
         <v>2</v>
       </c>
       <c r="B358" s="8" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C358" s="1">
         <v>8</v>
@@ -9804,7 +9804,7 @@
         <v>3</v>
       </c>
       <c r="B359" s="8" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C359" s="1">
         <v>8</v>
@@ -9831,7 +9831,7 @@
         <v>4</v>
       </c>
       <c r="B360" s="8" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C360" s="1">
         <v>8</v>
@@ -9858,7 +9858,7 @@
         <v>5</v>
       </c>
       <c r="B361" s="8" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C361" s="1">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>6</v>
       </c>
       <c r="B362" s="8" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C362" s="1">
         <v>0</v>
@@ -9912,7 +9912,7 @@
         <v>7</v>
       </c>
       <c r="B363" s="8" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C363" s="1">
         <v>2</v>
@@ -9939,7 +9939,7 @@
         <v>8</v>
       </c>
       <c r="B364" s="8" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C364" s="1">
         <v>8</v>
@@ -9966,7 +9966,7 @@
         <v>9</v>
       </c>
       <c r="B365" s="8" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C365" s="1">
         <v>8</v>
@@ -9993,7 +9993,7 @@
         <v>10</v>
       </c>
       <c r="B366" s="9" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C366" s="4">
         <v>0</v>
@@ -10035,7 +10035,7 @@
     <row r="368" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="369" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A369" s="10" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B369" s="11"/>
       <c r="C369" s="11"/>
@@ -10117,7 +10117,7 @@
         <v>2</v>
       </c>
       <c r="B373" s="8" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C373" s="1">
         <v>8</v>
@@ -10144,7 +10144,7 @@
         <v>3</v>
       </c>
       <c r="B374" s="8" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C374" s="1">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4</v>
       </c>
       <c r="B375" s="8" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C375" s="1">
         <v>5</v>
@@ -10198,7 +10198,7 @@
         <v>5</v>
       </c>
       <c r="B376" s="8" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C376" s="1">
         <v>5</v>
@@ -10225,7 +10225,7 @@
         <v>6</v>
       </c>
       <c r="B377" s="8" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C377" s="1">
         <v>5</v>
@@ -10252,7 +10252,7 @@
         <v>7</v>
       </c>
       <c r="B378" s="8" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C378" s="1">
         <v>5</v>
@@ -10279,7 +10279,7 @@
         <v>8</v>
       </c>
       <c r="B379" s="8" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C379" s="1">
         <v>1</v>
@@ -10306,7 +10306,7 @@
         <v>9</v>
       </c>
       <c r="B380" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C380" s="4">
         <v>0</v>
@@ -10348,7 +10348,7 @@
     <row r="382" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="383" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A383" s="10" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B383" s="11"/>
       <c r="C383" s="11"/>
@@ -10403,7 +10403,7 @@
         <v>1</v>
       </c>
       <c r="B386" s="7" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C386" s="19">
         <v>2</v>
@@ -10430,7 +10430,7 @@
         <v>2</v>
       </c>
       <c r="B387" s="8" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C387" s="1">
         <v>9</v>
@@ -10457,7 +10457,7 @@
         <v>3</v>
       </c>
       <c r="B388" s="8" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C388" s="1">
         <v>9</v>
@@ -10484,7 +10484,7 @@
         <v>4</v>
       </c>
       <c r="B389" s="8" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C389" s="1">
         <v>9</v>
@@ -10511,7 +10511,7 @@
         <v>5</v>
       </c>
       <c r="B390" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C390" s="1">
         <v>9</v>
@@ -10538,7 +10538,7 @@
         <v>6</v>
       </c>
       <c r="B391" s="8" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C391" s="1">
         <v>5</v>
@@ -10565,7 +10565,7 @@
         <v>7</v>
       </c>
       <c r="B392" s="8" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C392" s="1">
         <v>1</v>
@@ -10592,7 +10592,7 @@
         <v>8</v>
       </c>
       <c r="B393" s="8" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C393" s="1">
         <v>9</v>
@@ -10619,7 +10619,7 @@
         <v>9</v>
       </c>
       <c r="B394" s="8" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C394" s="1">
         <v>9</v>
@@ -10646,7 +10646,7 @@
         <v>10</v>
       </c>
       <c r="B395" s="8" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C395" s="1">
         <v>8</v>
@@ -10715,7 +10715,7 @@
     <row r="398" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="399" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A399" s="10" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B399" s="11"/>
       <c r="C399" s="11"/>
@@ -10770,7 +10770,7 @@
         <v>1</v>
       </c>
       <c r="B402" s="7" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C402" s="19">
         <v>7</v>
@@ -10791,7 +10791,7 @@
         <v>2</v>
       </c>
       <c r="B403" s="8" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C403" s="1">
         <v>3</v>
@@ -10812,7 +10812,7 @@
         <v>3</v>
       </c>
       <c r="B404" s="8" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C404" s="1">
         <v>7</v>
@@ -10833,7 +10833,7 @@
         <v>4</v>
       </c>
       <c r="B405" s="8" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C405" s="1">
         <v>7</v>
@@ -10854,7 +10854,7 @@
         <v>5</v>
       </c>
       <c r="B406" s="8" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C406" s="1">
         <v>7</v>
@@ -10875,7 +10875,7 @@
         <v>6</v>
       </c>
       <c r="B407" s="8" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C407" s="1">
         <v>7</v>
@@ -10896,7 +10896,7 @@
         <v>7</v>
       </c>
       <c r="B408" s="9" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C408" s="4">
         <v>7</v>
@@ -10932,7 +10932,7 @@
     <row r="410" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="411" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A411" s="10" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B411" s="11"/>
       <c r="C411" s="11"/>
@@ -10987,7 +10987,7 @@
         <v>1</v>
       </c>
       <c r="B414" s="7" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C414" s="19">
         <v>8</v>
@@ -11014,7 +11014,7 @@
         <v>2</v>
       </c>
       <c r="B415" s="8" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C415" s="1">
         <v>8</v>
@@ -11041,7 +11041,7 @@
         <v>3</v>
       </c>
       <c r="B416" s="8" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C416" s="1">
         <v>8</v>
@@ -11068,7 +11068,7 @@
         <v>4</v>
       </c>
       <c r="B417" s="8" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C417" s="1">
         <v>5</v>
@@ -11095,7 +11095,7 @@
         <v>5</v>
       </c>
       <c r="B418" s="8" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C418" s="1">
         <v>4</v>
@@ -11122,7 +11122,7 @@
         <v>6</v>
       </c>
       <c r="B419" s="8" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C419" s="1">
         <v>0</v>
@@ -11149,7 +11149,7 @@
         <v>7</v>
       </c>
       <c r="B420" s="8" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C420" s="1">
         <v>8</v>
@@ -11176,7 +11176,7 @@
         <v>8</v>
       </c>
       <c r="B421" s="8" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C421" s="1">
         <v>8</v>
@@ -11203,7 +11203,7 @@
         <v>9</v>
       </c>
       <c r="B422" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C422" s="1">
         <v>2</v>
@@ -11230,7 +11230,7 @@
         <v>10</v>
       </c>
       <c r="B423" s="8" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C423" s="1">
         <v>2</v>
@@ -11257,7 +11257,7 @@
         <v>11</v>
       </c>
       <c r="B424" s="9" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C424" s="4">
         <v>8</v>
@@ -11299,7 +11299,7 @@
     <row r="426" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="427" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A427" s="10" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B427" s="11"/>
       <c r="C427" s="11"/>
@@ -11354,7 +11354,7 @@
         <v>1</v>
       </c>
       <c r="B430" s="7" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C430" s="19">
         <v>8</v>
@@ -11381,7 +11381,7 @@
         <v>2</v>
       </c>
       <c r="B431" s="8" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C431" s="1">
         <v>8</v>
@@ -11408,7 +11408,7 @@
         <v>3</v>
       </c>
       <c r="B432" s="8" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C432" s="1">
         <v>4</v>
@@ -11435,7 +11435,7 @@
         <v>4</v>
       </c>
       <c r="B433" s="8" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C433" s="1">
         <v>8</v>
@@ -11462,7 +11462,7 @@
         <v>5</v>
       </c>
       <c r="B434" s="8" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C434" s="1">
         <v>8</v>
@@ -11489,7 +11489,7 @@
         <v>6</v>
       </c>
       <c r="B435" s="8" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C435" s="1">
         <v>0</v>
@@ -11516,7 +11516,7 @@
         <v>7</v>
       </c>
       <c r="B436" s="8" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C436" s="1">
         <v>2</v>
@@ -11543,7 +11543,7 @@
         <v>8</v>
       </c>
       <c r="B437" s="8" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C437" s="1">
         <v>7</v>
@@ -11570,7 +11570,7 @@
         <v>9</v>
       </c>
       <c r="B438" s="8" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C438" s="1">
         <v>8</v>
@@ -11597,7 +11597,7 @@
         <v>10</v>
       </c>
       <c r="B439" s="8" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C439" s="1">
         <v>1</v>
@@ -11624,7 +11624,7 @@
         <v>11</v>
       </c>
       <c r="B440" s="8" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C440" s="1">
         <v>1</v>
@@ -11651,7 +11651,7 @@
         <v>12</v>
       </c>
       <c r="B441" s="8" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C441" s="1">
         <v>8</v>
@@ -11678,7 +11678,7 @@
         <v>13</v>
       </c>
       <c r="B442" s="9" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C442" s="4">
         <v>2</v>
@@ -11720,7 +11720,7 @@
     <row r="444" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="445" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A445" s="10" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B445" s="11"/>
       <c r="C445" s="11"/>
@@ -11775,7 +11775,7 @@
         <v>1</v>
       </c>
       <c r="B448" s="7" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C448" s="19">
         <v>8</v>
@@ -11817,7 +11817,7 @@
         <v>3</v>
       </c>
       <c r="B450" s="8" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C450" s="1">
         <v>7</v>
@@ -11838,7 +11838,7 @@
         <v>4</v>
       </c>
       <c r="B451" s="8" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C451" s="1">
         <v>8</v>
@@ -11859,7 +11859,7 @@
         <v>5</v>
       </c>
       <c r="B452" s="8" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C452" s="1">
         <v>8</v>
@@ -11880,7 +11880,7 @@
         <v>6</v>
       </c>
       <c r="B453" s="8" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C453" s="1">
         <v>8</v>
@@ -11901,7 +11901,7 @@
         <v>7</v>
       </c>
       <c r="B454" s="8" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C454" s="1">
         <v>8</v>
@@ -11922,7 +11922,7 @@
         <v>8</v>
       </c>
       <c r="B455" s="8" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C455" s="1">
         <v>6</v>
@@ -11943,7 +11943,7 @@
         <v>9</v>
       </c>
       <c r="B456" s="8" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C456" s="1">
         <v>5</v>
@@ -11964,7 +11964,7 @@
         <v>10</v>
       </c>
       <c r="B457" s="9" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C457" s="4">
         <v>8</v>
@@ -12000,7 +12000,7 @@
     <row r="459" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="460" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A460" s="10" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B460" s="11"/>
       <c r="C460" s="11"/>
@@ -12055,7 +12055,7 @@
         <v>1</v>
       </c>
       <c r="B463" s="7" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C463" s="19">
         <v>7</v>
@@ -12082,7 +12082,7 @@
         <v>2</v>
       </c>
       <c r="B464" s="8" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C464" s="1">
         <v>2</v>
@@ -12109,7 +12109,7 @@
         <v>3</v>
       </c>
       <c r="B465" s="8" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C465" s="1">
         <v>5</v>
@@ -12136,7 +12136,7 @@
         <v>4</v>
       </c>
       <c r="B466" s="8" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C466" s="1">
         <v>8</v>
@@ -12163,7 +12163,7 @@
         <v>5</v>
       </c>
       <c r="B467" s="8" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C467" s="1">
         <v>7</v>
@@ -12190,7 +12190,7 @@
         <v>6</v>
       </c>
       <c r="B468" s="8" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C468" s="1">
         <v>8</v>
@@ -12217,7 +12217,7 @@
         <v>7</v>
       </c>
       <c r="B469" s="8" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C469" s="1">
         <v>8</v>
@@ -12244,7 +12244,7 @@
         <v>8</v>
       </c>
       <c r="B470" s="8" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C470" s="1">
         <v>7</v>
@@ -12271,7 +12271,7 @@
         <v>9</v>
       </c>
       <c r="B471" s="9" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C471" s="4">
         <v>7</v>
@@ -12313,7 +12313,7 @@
     <row r="473" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="474" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A474" s="10" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B474" s="11"/>
       <c r="C474" s="11"/>
@@ -12368,7 +12368,7 @@
         <v>1</v>
       </c>
       <c r="B477" s="7" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C477" s="19">
         <v>8</v>
@@ -12395,7 +12395,7 @@
         <v>2</v>
       </c>
       <c r="B478" s="8" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C478" s="1">
         <v>8</v>
@@ -12422,7 +12422,7 @@
         <v>3</v>
       </c>
       <c r="B479" s="8" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C479" s="1">
         <v>4</v>
@@ -12449,7 +12449,7 @@
         <v>4</v>
       </c>
       <c r="B480" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C480" s="1">
         <v>4</v>
@@ -12476,7 +12476,7 @@
         <v>5</v>
       </c>
       <c r="B481" s="8" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C481" s="1">
         <v>8</v>
@@ -12503,7 +12503,7 @@
         <v>6</v>
       </c>
       <c r="B482" s="8" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C482" s="1">
         <v>3</v>
@@ -12530,7 +12530,7 @@
         <v>7</v>
       </c>
       <c r="B483" s="8" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C483" s="1">
         <v>7</v>
@@ -12557,7 +12557,7 @@
         <v>8</v>
       </c>
       <c r="B484" s="8" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C484" s="1">
         <v>3</v>
@@ -12584,7 +12584,7 @@
         <v>9</v>
       </c>
       <c r="B485" s="8" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C485" s="1">
         <v>7</v>
@@ -12611,7 +12611,7 @@
         <v>10</v>
       </c>
       <c r="B486" s="8" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C486" s="1">
         <v>7</v>
@@ -12638,7 +12638,7 @@
         <v>11</v>
       </c>
       <c r="B487" s="9" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C487" s="4">
         <v>8</v>
@@ -12680,7 +12680,7 @@
     <row r="489" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="490" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A490" s="10" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B490" s="11"/>
       <c r="C490" s="11"/>
@@ -12735,7 +12735,7 @@
         <v>1</v>
       </c>
       <c r="B493" s="7" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C493" s="19">
         <v>8</v>
@@ -12762,7 +12762,7 @@
         <v>2</v>
       </c>
       <c r="B494" s="8" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C494" s="1">
         <v>6</v>
@@ -12789,7 +12789,7 @@
         <v>3</v>
       </c>
       <c r="B495" s="8" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C495" s="1">
         <v>8</v>
@@ -12816,7 +12816,7 @@
         <v>4</v>
       </c>
       <c r="B496" s="8" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C496" s="1">
         <v>4</v>
@@ -12843,7 +12843,7 @@
         <v>5</v>
       </c>
       <c r="B497" s="8" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C497" s="1">
         <v>8</v>
@@ -12870,7 +12870,7 @@
         <v>6</v>
       </c>
       <c r="B498" s="8" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C498" s="1">
         <v>4</v>
@@ -12897,7 +12897,7 @@
         <v>7</v>
       </c>
       <c r="B499" s="8" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C499" s="1">
         <v>8</v>
@@ -12924,7 +12924,7 @@
         <v>8</v>
       </c>
       <c r="B500" s="8" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C500" s="1">
         <v>8</v>
@@ -12951,7 +12951,7 @@
         <v>9</v>
       </c>
       <c r="B501" s="8" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C501" s="1">
         <v>8</v>
@@ -12978,7 +12978,7 @@
         <v>10</v>
       </c>
       <c r="B502" s="8" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C502" s="1">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>11</v>
       </c>
       <c r="B503" s="8" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C503" s="1">
         <v>0</v>
@@ -13032,7 +13032,7 @@
         <v>12</v>
       </c>
       <c r="B504" s="8" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C504" s="1">
         <v>8</v>
@@ -13059,7 +13059,7 @@
         <v>13</v>
       </c>
       <c r="B505" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C505" s="1">
         <v>0</v>
@@ -13086,7 +13086,7 @@
         <v>14</v>
       </c>
       <c r="B506" s="9" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C506" s="4">
         <v>8</v>
@@ -13128,7 +13128,7 @@
     <row r="508" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="509" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A509" s="10" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B509" s="11"/>
       <c r="C509" s="11"/>
@@ -13183,7 +13183,7 @@
         <v>1</v>
       </c>
       <c r="B512" s="7" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C512" s="19">
         <v>7</v>
@@ -13210,7 +13210,7 @@
         <v>2</v>
       </c>
       <c r="B513" s="8" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C513" s="1">
         <v>8</v>
@@ -13237,7 +13237,7 @@
         <v>3</v>
       </c>
       <c r="B514" s="8" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C514" s="1">
         <v>8</v>
@@ -13264,7 +13264,7 @@
         <v>4</v>
       </c>
       <c r="B515" s="8" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C515" s="1">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>5</v>
       </c>
       <c r="B516" s="8" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C516" s="1">
         <v>3</v>
@@ -13318,7 +13318,7 @@
         <v>6</v>
       </c>
       <c r="B517" s="8" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C517" s="1">
         <v>1</v>
@@ -13345,7 +13345,7 @@
         <v>7</v>
       </c>
       <c r="B518" s="8" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C518" s="1">
         <v>8</v>
@@ -13372,7 +13372,7 @@
         <v>8</v>
       </c>
       <c r="B519" s="8" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C519" s="1">
         <v>8</v>
@@ -13399,7 +13399,7 @@
         <v>9</v>
       </c>
       <c r="B520" s="8" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C520" s="1">
         <v>4</v>
@@ -13426,7 +13426,7 @@
         <v>10</v>
       </c>
       <c r="B521" s="9" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C521" s="4">
         <v>2</v>
@@ -13468,7 +13468,7 @@
     <row r="523" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="524" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A524" s="10" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B524" s="11"/>
       <c r="C524" s="11"/>
@@ -13523,7 +13523,7 @@
         <v>1</v>
       </c>
       <c r="B527" s="7" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C527" s="1">
         <v>8</v>
@@ -13544,7 +13544,7 @@
         <v>2</v>
       </c>
       <c r="B528" s="8" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C528">
         <v>5</v>
@@ -13565,7 +13565,7 @@
         <v>3</v>
       </c>
       <c r="B529" s="8" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C529" s="1">
         <v>7</v>
@@ -13586,7 +13586,7 @@
         <v>4</v>
       </c>
       <c r="B530" s="8" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C530" s="1">
         <v>2</v>
@@ -13607,7 +13607,7 @@
         <v>5</v>
       </c>
       <c r="B531" s="8" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C531" s="1">
         <v>2</v>
@@ -13628,7 +13628,7 @@
         <v>6</v>
       </c>
       <c r="B532" s="8" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C532" s="1">
         <v>6</v>
@@ -13649,7 +13649,7 @@
         <v>7</v>
       </c>
       <c r="B533" s="8" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C533" s="1">
         <v>7</v>
@@ -13670,7 +13670,7 @@
         <v>8</v>
       </c>
       <c r="B534" s="8" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C534" s="1">
         <v>8</v>
@@ -13691,7 +13691,7 @@
         <v>9</v>
       </c>
       <c r="B535" s="8" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C535" s="1">
         <v>6</v>
@@ -13712,7 +13712,7 @@
         <v>10</v>
       </c>
       <c r="B536" s="9" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C536" s="4">
         <v>6</v>
@@ -13748,7 +13748,7 @@
     <row r="538" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="539" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A539" s="10" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B539" s="11"/>
       <c r="C539" s="11"/>
@@ -13803,7 +13803,7 @@
         <v>1</v>
       </c>
       <c r="B542" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C542" s="19">
         <v>8</v>
@@ -13830,7 +13830,7 @@
         <v>2</v>
       </c>
       <c r="B543" s="8" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C543" s="2">
         <v>8</v>
@@ -13857,7 +13857,7 @@
         <v>3</v>
       </c>
       <c r="B544" s="8" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C544" s="1">
         <v>8</v>
@@ -13884,7 +13884,7 @@
         <v>4</v>
       </c>
       <c r="B545" s="8" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C545" s="1">
         <v>8</v>
@@ -13911,7 +13911,7 @@
         <v>5</v>
       </c>
       <c r="B546" s="8" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C546" s="1">
         <v>8</v>
@@ -13938,7 +13938,7 @@
         <v>6</v>
       </c>
       <c r="B547" s="8" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C547" s="1">
         <v>8</v>
@@ -13965,7 +13965,7 @@
         <v>7</v>
       </c>
       <c r="B548" s="8" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C548" s="1">
         <v>8</v>
@@ -13992,7 +13992,7 @@
         <v>8</v>
       </c>
       <c r="B549" s="8" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C549" s="1">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>9</v>
       </c>
       <c r="B550" s="8" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C550" s="1">
         <v>2</v>
@@ -14046,7 +14046,7 @@
         <v>10</v>
       </c>
       <c r="B551" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C551" s="4">
         <v>0</v>
@@ -14088,7 +14088,7 @@
     <row r="553" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="554" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A554" s="10" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B554" s="11"/>
       <c r="C554" s="11"/>
@@ -14143,7 +14143,7 @@
         <v>1</v>
       </c>
       <c r="B557" s="7" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C557" s="19">
         <v>8</v>
@@ -14170,7 +14170,7 @@
         <v>2</v>
       </c>
       <c r="B558" s="8" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C558" s="2">
         <v>8</v>
@@ -14197,7 +14197,7 @@
         <v>3</v>
       </c>
       <c r="B559" s="8" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C559" s="1">
         <v>8</v>
@@ -14224,7 +14224,7 @@
         <v>4</v>
       </c>
       <c r="B560" s="8" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C560" s="1">
         <v>8</v>
@@ -14251,7 +14251,7 @@
         <v>5</v>
       </c>
       <c r="B561" s="8" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C561" s="1">
         <v>8</v>
@@ -14278,7 +14278,7 @@
         <v>6</v>
       </c>
       <c r="B562" s="8" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C562" s="1">
         <v>4</v>
@@ -14305,7 +14305,7 @@
         <v>7</v>
       </c>
       <c r="B563" s="8" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C563" s="1">
         <v>8</v>
@@ -14332,7 +14332,7 @@
         <v>8</v>
       </c>
       <c r="B564" s="8" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C564" s="1">
         <v>2</v>
@@ -14359,7 +14359,7 @@
         <v>9</v>
       </c>
       <c r="B565" s="8" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C565" s="1">
         <v>1</v>
@@ -14386,7 +14386,7 @@
         <v>10</v>
       </c>
       <c r="B566" s="9" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C566" s="4">
         <v>2</v>
@@ -14428,7 +14428,7 @@
     <row r="568" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="569" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A569" s="10" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B569" s="11"/>
       <c r="C569" s="11"/>
@@ -14483,7 +14483,7 @@
         <v>1</v>
       </c>
       <c r="B572" s="7" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C572" s="19">
         <v>8</v>
@@ -14510,7 +14510,7 @@
         <v>2</v>
       </c>
       <c r="B573" s="8" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C573" s="1">
         <v>8</v>
@@ -14537,7 +14537,7 @@
         <v>3</v>
       </c>
       <c r="B574" s="8" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C574" s="1">
         <v>8</v>
@@ -14564,7 +14564,7 @@
         <v>4</v>
       </c>
       <c r="B575" s="8" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C575" s="1">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5</v>
       </c>
       <c r="B576" s="8" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C576" s="1">
         <v>8</v>
@@ -14618,7 +14618,7 @@
         <v>6</v>
       </c>
       <c r="B577" s="8" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C577" s="1">
         <v>2</v>
@@ -14645,7 +14645,7 @@
         <v>7</v>
       </c>
       <c r="B578" s="8" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C578" s="1">
         <v>8</v>
@@ -14672,7 +14672,7 @@
         <v>8</v>
       </c>
       <c r="B579" s="8" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C579" s="1">
         <v>0</v>
@@ -14699,7 +14699,7 @@
         <v>9</v>
       </c>
       <c r="B580" s="8" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C580" s="1">
         <v>8</v>
@@ -14726,7 +14726,7 @@
         <v>10</v>
       </c>
       <c r="B581" s="8" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C581" s="1">
         <v>2</v>
@@ -14753,7 +14753,7 @@
         <v>11</v>
       </c>
       <c r="B582" s="9" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C582" s="4">
         <v>8</v>
@@ -14795,7 +14795,7 @@
     <row r="584" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="585" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A585" s="10" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B585" s="11"/>
       <c r="C585" s="11"/>
@@ -14850,7 +14850,7 @@
         <v>1</v>
       </c>
       <c r="B588" s="7" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C588" s="19">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2</v>
       </c>
       <c r="B589" s="8" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C589" s="1">
         <v>8</v>
@@ -14904,7 +14904,7 @@
         <v>3</v>
       </c>
       <c r="B590" s="8" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C590" s="1">
         <v>8</v>
@@ -14931,7 +14931,7 @@
         <v>4</v>
       </c>
       <c r="B591" s="8" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C591" s="1">
         <v>8</v>
@@ -14958,7 +14958,7 @@
         <v>5</v>
       </c>
       <c r="B592" s="8" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C592" s="1">
         <v>6</v>
@@ -14985,7 +14985,7 @@
         <v>6</v>
       </c>
       <c r="B593" s="8" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C593" s="1">
         <v>6</v>
@@ -15012,7 +15012,7 @@
         <v>7</v>
       </c>
       <c r="B594" s="8" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C594" s="1">
         <v>8</v>
@@ -15039,7 +15039,7 @@
         <v>8</v>
       </c>
       <c r="B595" s="8" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C595" s="1">
         <v>0</v>
@@ -15066,7 +15066,7 @@
         <v>9</v>
       </c>
       <c r="B596" s="8" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C596" s="1">
         <v>8</v>
@@ -15093,7 +15093,7 @@
         <v>10</v>
       </c>
       <c r="B597" s="8" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C597" s="1">
         <v>8</v>
@@ -15120,7 +15120,7 @@
         <v>11</v>
       </c>
       <c r="B598" s="9" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C598" s="4">
         <v>2</v>
@@ -15162,7 +15162,7 @@
     <row r="600" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="601" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A601" s="10" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B601" s="11"/>
       <c r="C601" s="11"/>
@@ -15217,7 +15217,7 @@
         <v>1</v>
       </c>
       <c r="B604" s="7" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C604" s="19">
         <v>6</v>
@@ -15238,7 +15238,7 @@
         <v>2</v>
       </c>
       <c r="B605" s="8" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C605" s="1">
         <v>6</v>
@@ -15259,7 +15259,7 @@
         <v>3</v>
       </c>
       <c r="B606" s="8" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C606" s="1">
         <v>8</v>
@@ -15280,7 +15280,7 @@
         <v>4</v>
       </c>
       <c r="B607" s="8" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C607" s="1">
         <v>8</v>
@@ -15301,7 +15301,7 @@
         <v>5</v>
       </c>
       <c r="B608" s="8" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C608" s="1">
         <v>2</v>
@@ -15322,7 +15322,7 @@
         <v>6</v>
       </c>
       <c r="B609" s="8" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C609" s="1">
         <v>8</v>
@@ -15343,7 +15343,7 @@
         <v>7</v>
       </c>
       <c r="B610" s="9" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C610" s="4">
         <v>6</v>
@@ -15447,24 +15447,24 @@
     <mergeCell ref="A283:H283"/>
     <mergeCell ref="C284:E284"/>
     <mergeCell ref="F284:H284"/>
-    <mergeCell ref="A235:H235"/>
-    <mergeCell ref="C236:E236"/>
-    <mergeCell ref="F236:H236"/>
-    <mergeCell ref="A248:H248"/>
-    <mergeCell ref="C249:E249"/>
-    <mergeCell ref="F249:H249"/>
-    <mergeCell ref="A201:H201"/>
-    <mergeCell ref="C202:E202"/>
-    <mergeCell ref="F202:H202"/>
-    <mergeCell ref="A218:H218"/>
-    <mergeCell ref="C219:E219"/>
-    <mergeCell ref="F219:H219"/>
+    <mergeCell ref="A234:H234"/>
+    <mergeCell ref="C235:E235"/>
+    <mergeCell ref="F235:H235"/>
+    <mergeCell ref="A247:H247"/>
+    <mergeCell ref="C248:E248"/>
+    <mergeCell ref="F248:H248"/>
+    <mergeCell ref="A200:H200"/>
+    <mergeCell ref="C201:E201"/>
+    <mergeCell ref="F201:H201"/>
+    <mergeCell ref="A217:H217"/>
+    <mergeCell ref="C218:E218"/>
+    <mergeCell ref="F218:H218"/>
     <mergeCell ref="A160:H160"/>
     <mergeCell ref="C161:E161"/>
     <mergeCell ref="F161:H161"/>
-    <mergeCell ref="A182:H182"/>
-    <mergeCell ref="C183:E183"/>
-    <mergeCell ref="F183:H183"/>
+    <mergeCell ref="A181:H181"/>
+    <mergeCell ref="C182:E182"/>
+    <mergeCell ref="F182:H182"/>
     <mergeCell ref="A129:H129"/>
     <mergeCell ref="C130:E130"/>
     <mergeCell ref="F130:H130"/>
